--- a/dotnet_jobs_20260327_091000.xlsx
+++ b/dotnet_jobs_20260327_091000.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>2026-03-27 09:41</t>
+          <t>2026-03-30 23:47</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
